--- a/src/attributions/attributions_ig_traj_307.xlsx
+++ b/src/attributions/attributions_ig_traj_307.xlsx
@@ -2137,25 +2137,25 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02969514980026365</v>
+        <v>0.04838647055759854</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.004486745018263861</v>
+        <v>-0.001786819170494007</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01719697832880843</v>
+        <v>-0.04045309296367253</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2164,28 +2164,28 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000995458900882529</v>
+        <v>0.00434925326816464</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0002212138752041233</v>
+        <v>-7.83215777860344e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001710711477216274</v>
+        <v>0.003362067128259772</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-0</v>
@@ -2194,76 +2194,76 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.109449524723543e-05</v>
+        <v>0.006524124896037748</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003160095687536489</v>
+        <v>0.01912316791954533</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.004624921247498804</v>
+        <v>0.00724582027256844</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.007898014378788929</v>
+        <v>-0.04350936210053551</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02304711119329559</v>
+        <v>-0.04923434876205939</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.001731884852654782</v>
+        <v>-0.0318008326706462</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.007918027694342938</v>
+        <v>-0.007774968862087686</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.009281476449933847</v>
+        <v>-0.03783732017712241</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.01009388664139005</v>
+        <v>-0.03482038582473217</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2272,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.04545918911434506</v>
+        <v>0.2275504674332076</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,10 +2284,10 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.005213439503410523</v>
+        <v>-0.03663250913280463</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.03200717590618507</v>
+        <v>-0.05695405544916757</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,67 +2296,67 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.00414414005314921</v>
+        <v>-0.00324348598636104</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.001853318137774226</v>
+        <v>-0.003829390446940117</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.004700110402797208</v>
+        <v>0.01360698108933656</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.01587693591355116</v>
+        <v>0.04050825321864131</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.002017422009749032</v>
+        <v>0.06541382070024737</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.009842470015132384</v>
+        <v>0.07258985088233862</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02544299720829586</v>
+        <v>0.07307159738187913</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,25 +2365,25 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.007718301935350859</v>
+        <v>-0.04614121210105208</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004094054963969077</v>
+        <v>-0.07433024148335349</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.006949020323401893</v>
+        <v>-0.02960403058241843</v>
       </c>
       <c r="CF4" t="n">
         <v>-0</v>
@@ -2392,25 +2392,25 @@
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.003263976160732877</v>
+        <v>0.003312442640315963</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0213173417865518</v>
+        <v>0.05704024881181525</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001045290382101205</v>
+        <v>-0.07269417548144243</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
@@ -2419,25 +2419,25 @@
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.006225117131420544</v>
+        <v>0.05904484815373719</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.004104885781784253</v>
+        <v>0.04460431718841384</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
         <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.005981501360788912</v>
+        <v>-0.03792112097970082</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
@@ -2446,37 +2446,37 @@
         <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.003391290869759487</v>
+        <v>-0.008707779350566654</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.02324088206781732</v>
+        <v>0.05322745102148122</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
         <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.007713576291191954</v>
+        <v>-0.005128267249030228</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0132846631427953</v>
+        <v>-0.02489393363798087</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.035598951715859</v>
+        <v>0.0210178013450732</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,28 +2485,28 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.003147041629658409</v>
+        <v>-0.01515336455102573</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.007283072500700987</v>
+        <v>0.01592025148171499</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.001636112243406158</v>
+        <v>0.07757127116633707</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,73 +2518,73 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.00149323182908096</v>
+        <v>0.01944648857831652</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01344700830368035</v>
+        <v>-0.05495618125629937</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.01514828799119386</v>
+        <v>-0.05428730992650876</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.001998085287271559</v>
+        <v>-0.03169105707500686</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.003753074547703528</v>
+        <v>-0.04100723078067089</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01339623832889249</v>
+        <v>0.02096089492310487</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.002394827748072403</v>
+        <v>0.02232925394922217</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.007533837930613212</v>
+        <v>-0.04373480117339904</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.02542276346619891</v>
+        <v>0.0413966923223535</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
@@ -2596,10 +2596,10 @@
         <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.006123974299486021</v>
+        <v>-0.03850995063531263</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,25 +2608,25 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.001253792632046002</v>
+        <v>-0.01478717423795507</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.02316533334160216</v>
+        <v>0.04547125381248475</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.007115951728552341</v>
+        <v>-0.05266157380732957</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01719170186447725</v>
+        <v>0.006137902174093306</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.004031205109718479</v>
+        <v>-0.03002911314102863</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-7.660029906549855e-05</v>
+        <v>0.03680235821099613</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.01064915001598695</v>
+        <v>0.01505922288971257</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.01073786629341293</v>
+        <v>0.02458273083290072</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,13 +2674,13 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.0158469842819973</v>
+        <v>-0.002997170805822051</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2689,10 +2689,10 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.007073980298240037</v>
+        <v>0.03632695881722338</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06876213652894703</v>
+        <v>0.1621356426690825</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01612815102021767</v>
+        <v>-0.05202841742436298</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002808990262324953</v>
+        <v>-0.04224052450246578</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,16 +2736,16 @@
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005348368308062218</v>
+        <v>0.01998527450252835</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02623051485673623</v>
+        <v>0.106089167134664</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.001547194081164358</v>
+        <v>-0.003386176227133595</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,127 +2760,127 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.508269395543428e-11</v>
+        <v>2.78372785870698e-11</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.328077162209247e-12</v>
+        <v>9.810510306168124e-12</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.006837434204491936</v>
+        <v>-0.003455942933548638</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.001688900280018908</v>
+        <v>-0.01230348787597439</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.02590951571714332</v>
+        <v>-0.07366044541594215</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.06481564484552887</v>
+        <v>-0.04457207092186955</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.01879148084783806</v>
+        <v>0.094388038129503</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.03663586849981307</v>
+        <v>-0.01712566686229914</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.0361249540426402</v>
+        <v>0.06207564547294376</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.2518633586709244</v>
+        <v>0.2982779823041237</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0554860743980533</v>
+        <v>-0.164115638687233</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2133604188435684</v>
+        <v>-0.148335872744585</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.00940417451876001</v>
+        <v>-0.003985732928707978</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.012278206238095</v>
+        <v>0.001154427370658405</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.007395050626148657</v>
+        <v>-0.0002804895664951684</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.04756595981204344</v>
+        <v>-0.02475077769036256</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.04383435143358739</v>
+        <v>0.06159516193593088</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1267972614703599</v>
+        <v>0.08373934058139523</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,46 +2925,46 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1222635253488253</v>
+        <v>0.208749805311324</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.03595073671729555</v>
+        <v>-0.1135924165915857</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.05741408408257113</v>
+        <v>0.0006098631426345394</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.02532027502810223</v>
+        <v>-0.1110405244855273</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.006988755444866572</v>
+        <v>0.08391147043827839</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.01485244768155236</v>
+        <v>0.0165036708292764</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
@@ -2979,16 +2979,16 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.02355927393085766</v>
+        <v>-0.09878628194101646</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.03960289029185005</v>
+        <v>0.04508026998630506</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1161819533664464</v>
+        <v>-0.009163159554236674</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
@@ -3003,22 +3003,22 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.0185859622318724</v>
+        <v>-0.1198549936265539</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.01839643908934938</v>
+        <v>0.09456459483591298</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01077584923813823</v>
+        <v>0.02025382539537298</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
@@ -3030,106 +3030,106 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.0009898906573493583</v>
+        <v>-0.006025428505165076</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.007166605759904453</v>
+        <v>0.0413959625639639</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.04738431952502015</v>
+        <v>-0.05760806780262553</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.06683471257346327</v>
+        <v>-0.05030247901405866</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.002055971274143149</v>
+        <v>0.01433331968181826</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01529296677809208</v>
+        <v>-0.06228871370408487</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.007661080218687115</v>
+        <v>0.06411919233083488</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.04169027455175969</v>
+        <v>0.04019844770531502</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01048847026781258</v>
+        <v>-0.02463044235816463</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.02231135890898016</v>
+        <v>-0.06147094347981374</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.003757076988285717</v>
+        <v>0.1058733432615646</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.03003038569464935</v>
+        <v>0.03758358691672524</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0442669368073742</v>
+        <v>-0.06875779837807322</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.01983877682190078</v>
+        <v>0.06645321237355156</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.01339207609257469</v>
+        <v>-0.04959676068619576</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>-0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.02503750585971114</v>
+        <v>-0.1300199035343492</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.01761498696429573</v>
+        <v>0.1044613695248296</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.007737598183185095</v>
+        <v>0.007292607879399378</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,46 +3192,46 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.05567249366283704</v>
+        <v>-0.06455616488187094</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.0406595776242947</v>
+        <v>-0.04033135172806136</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.006931789511214997</v>
+        <v>0.07592573315303032</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.0835444876447031</v>
+        <v>0.04064135645979622</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.02680894549190627</v>
+        <v>0.1334261094012096</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.05589604974083972</v>
+        <v>-0.07086452961374537</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
@@ -3240,28 +3240,28 @@
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01092706872107285</v>
+        <v>-0.08990989719049958</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.02292027342120366</v>
+        <v>0.03082105104059609</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01432242177052555</v>
+        <v>0.03110730780666478</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.006891135521011303</v>
+        <v>0.004333975546978828</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001158932283097279</v>
+        <v>-0.003051515135631801</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -3302,25 +3302,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002133638120864065</v>
+        <v>0.01581112682481572</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.001239726777491544</v>
+        <v>0.0003499021122532508</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003793241641486043</v>
+        <v>0.008541230376929365</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0002453440841823823</v>
+        <v>-0.001255000321417869</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-6.202833136213517e-12</v>
+        <v>-1.512742848004613e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.002812646137493388</v>
+        <v>0.0003840404862829447</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.00688588705220365</v>
+        <v>-0.01686314932378061</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.008372126765509438</v>
+        <v>-0.05145324523195081</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001491887289928304</v>
+        <v>-0.01788208424823647</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,46 +3386,46 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.003993718619250962</v>
+        <v>0.01305984940170519</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01497239025211313</v>
+        <v>-0.009122196191745211</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.005026257424436346</v>
+        <v>-0.02443844044044553</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.03676460748004197</v>
+        <v>0.1000999373147864</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.007064512898851071</v>
+        <v>-0.02375242955438277</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.00791522144556797</v>
+        <v>-0.01685228806899517</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3437,10 +3437,10 @@
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0005438150195778849</v>
+        <v>-0.003130249412872296</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,52 +3449,52 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.003346568201869502</v>
+        <v>-0.003204962048301293</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.001510548870458492</v>
+        <v>0.01139107570051305</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.01778868375538742</v>
+        <v>0.01278785690244897</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.009779921830411271</v>
+        <v>0.04493224962020218</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.008515868169613208</v>
+        <v>0.03411278005147229</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01539176956394893</v>
+        <v>0.03473063361224647</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.008224831419583013</v>
+        <v>-0.007594282129059502</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01798478344066243</v>
+        <v>-0.02846951194379503</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0002017503894488732</v>
+        <v>-0.01441743008969737</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
         <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.001101709752751596</v>
+        <v>0.003884876085894444</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.00448193046026499</v>
+        <v>0.02002813360930891</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3545,55 +3545,55 @@
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.006449168567970616</v>
+        <v>-0.01902025350301068</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.003333902294000641</v>
+        <v>0.03809298577824365</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01667966131684445</v>
+        <v>0.02262043844626023</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.002349021985068821</v>
+        <v>-0.01535536617890799</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.001376518697466045</v>
+        <v>0.0008517680525638021</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.006116646866970757</v>
+        <v>0.01869697617149378</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
@@ -3602,19 +3602,19 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0009758611068783462</v>
+        <v>-0.01051020551553798</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0005304288670825896</v>
+        <v>-0.0005559180694907556</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.008939932212949107</v>
+        <v>-0.007557750446854958</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,31 +3623,31 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.005520081808699989</v>
+        <v>-0.01265228644359322</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01052508930434323</v>
+        <v>2.973897101666315e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.003355822929152804</v>
+        <v>0.03476293396952797</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,7 +3656,7 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.009958882298008119</v>
+        <v>0.0102171049928527</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,40 +3665,40 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.01028715290693792</v>
+        <v>-0.01432007488699534</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.003446245890544093</v>
+        <v>0.0235184600396438</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.002007316221428888</v>
+        <v>-0.004646363660362187</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.002414588053547012</v>
+        <v>-0.008122369325465723</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.003485046009578796</v>
+        <v>-0.002870739659456422</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM6" t="n">
         <v>0</v>
@@ -3707,37 +3707,37 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.001534101270127171</v>
+        <v>0.002190110638375589</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.009658325154665375</v>
+        <v>-0.01558715664375795</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03123596795812238</v>
+        <v>0.01767061562276812</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.004797759464223349</v>
+        <v>-0.01831091338990358</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,37 +3746,37 @@
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.001598500452954259</v>
+        <v>-0.003974521812928161</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.006783538834071758</v>
+        <v>0.01389426787490035</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.009911897312155199</v>
+        <v>-0.01151183993715892</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01147840097291758</v>
+        <v>0.01657230165033123</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02185139037806209</v>
+        <v>0.009993407910390269</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3788,10 +3788,10 @@
         <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.003723646710280722</v>
+        <v>0.0180470385684799</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.002021109547973717</v>
+        <v>0.001092652251140258</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0.0005372728915117822</v>
+        <v>-0.0380333154458533</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,31 +3812,31 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.009221571378241287</v>
+        <v>0.002075676951602595</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.001816382616496545</v>
+        <v>0.007326335493281952</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.066102478458339</v>
+        <v>0.04673549045239181</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01997260894248171</v>
+        <v>-0.01387125210505739</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.760667006238202e-11</v>
+        <v>-7.042954603381673e-12</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01349853978260509</v>
+        <v>0.02594153467454676</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.003768872141558511</v>
+        <v>-0.006031823933203075</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3895,49 +3895,49 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02186714656949694</v>
+        <v>0.002346606601428981</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001156453374975741</v>
+        <v>-0.002047966202155298</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0005240181699380045</v>
+        <v>-0.003180054540906312</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001998320448781674</v>
+        <v>0.0006960066192203404</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02492534655493323</v>
+        <v>-0.02138250768291268</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02995938866300888</v>
+        <v>-0.02744511056070834</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.009372256834828934</v>
+        <v>-6.426950474864118e-05</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01546645709585602</v>
+        <v>0.02975726346447314</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,34 +3964,34 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01439277800885131</v>
+        <v>-0.007096241738414942</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01834733146567101</v>
+        <v>-0.01188963922290021</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1438000879825524</v>
+        <v>0.1063279826291991</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.09595247938855604</v>
+        <v>-0.02460324159105684</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4003,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.02593839994522229</v>
+        <v>0.008670945206853341</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.001638265801760188</v>
+        <v>-0.003683451888192819</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.009798979483219181</v>
+        <v>-0.004834289395556958</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,16 +4027,16 @@
         <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.02708521497954778</v>
+        <v>0.0150685322682401</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.003267597334671503</v>
+        <v>0.01175264318261389</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
@@ -4045,64 +4045,64 @@
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.07412236407375107</v>
+        <v>0.03937266719794703</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02641003108635615</v>
+        <v>0.01202064972159501</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05907292461921917</v>
+        <v>0.0585208359958543</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.03556476948155164</v>
+        <v>-0.01837768099449233</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.001624844515778495</v>
+        <v>-0.01664907952492743</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.01737075351526061</v>
+        <v>-0.02443462958018053</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.01351193352825577</v>
+        <v>0.004885123282306803</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.02970867540464687</v>
+        <v>0.01045615089933207</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01723296925065886</v>
+        <v>-0.03646717973799582</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.02406078838735803</v>
+        <v>0.004452017705611617</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,121 +4138,121 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.003358666322053761</v>
+        <v>0.02525136488122237</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01680161759039375</v>
+        <v>-0.02535019838999983</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.004907895274969732</v>
+        <v>0.003818338814866646</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.02660617992508643</v>
+        <v>0.009266588470867898</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.05804849551601477</v>
+        <v>-0.01382332295758834</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02147283819405433</v>
+        <v>-0.006551350646951497</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.01298170024929077</v>
+        <v>-0.009705612243966955</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.006780488781099211</v>
+        <v>-0.02042800331788979</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.003894647927624582</v>
+        <v>0.008164680393456449</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.004003866685450662</v>
+        <v>-0.02834101188773998</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.005997565326248757</v>
+        <v>0.01469834127792956</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.008594015102501192</v>
+        <v>-0.007781827390719177</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.02094562023610451</v>
+        <v>0.002507764704074898</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0006668896134091063</v>
+        <v>-0.01678382753602387</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
@@ -4261,52 +4261,52 @@
         <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.006633117675729111</v>
+        <v>-0.004276340012761922</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0287665911152565</v>
+        <v>0.003096184891174148</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.04450452663780904</v>
+        <v>-0.00410881063593265</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.006535275016636543</v>
+        <v>0.0009851922533887834</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.009997608858167681</v>
+        <v>0.006854763552596888</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02567459928894157</v>
+        <v>-0.02822697530502326</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.005908948459455067</v>
+        <v>-0.002245446660044322</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4324,25 +4324,25 @@
         <v>-0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.02122067654768708</v>
+        <v>0.01031885086035753</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01200839104145626</v>
+        <v>-0.01321290506182463</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02417294508896276</v>
+        <v>-0.002010248670421896</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01190400724040795</v>
+        <v>0.04852219100688614</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.03988401195279088</v>
+        <v>0.002157069548288852</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,7 +4369,7 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.003708907317445228</v>
+        <v>-0.00757867872794225</v>
       </c>
       <c r="FU7" t="n">
         <v>0</v>
@@ -4381,16 +4381,16 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-0.0003263635114416946</v>
+        <v>0.00115336866396375</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03788041318586152</v>
+        <v>-0.01090726821879794</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.01440004061493411</v>
+        <v>0.004336062374085878</v>
       </c>
     </row>
     <row r="8">
@@ -4985,43 +4985,43 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2538505589018548</v>
+        <v>0.1526652938567017</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1110481308469266</v>
+        <v>-0.1036379211942474</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0480479625146493</v>
+        <v>-0.05210020999759568</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08227274662137435</v>
+        <v>0.07313432666323816</v>
       </c>
       <c r="L9" t="n">
         <v>-0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.01996565398912678</v>
+        <v>-0.02751443831714103</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.03169723410482412</v>
+        <v>-0.04476373045003516</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5036,28 +5036,28 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01785629528759005</v>
+        <v>0.0298632792318229</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.007225872781135916</v>
+        <v>-0.002641048951514041</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.00822389445551846</v>
+        <v>-0.004925356112848256</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,43 +5066,43 @@
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.08612236245156608</v>
+        <v>0.01375741643179831</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.04082345659534814</v>
+        <v>-0.0957862992802415</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.04460945699186024</v>
+        <v>-0.1223320574563428</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01062452521099257</v>
+        <v>0.1466875432929144</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03416361520210508</v>
+        <v>-0.08417828136484294</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1079238646843149</v>
+        <v>0.05786304075308617</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,22 +5120,22 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.40963865824607</v>
+        <v>0.2741401225679219</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.03071796476465067</v>
+        <v>-0.08102665891550297</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1280069375471803</v>
+        <v>-0.3128954418546005</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -5144,19 +5144,19 @@
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.02345665791112443</v>
+        <v>-0.02523710805282428</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.02476937837256375</v>
+        <v>-0.0004011634040612271</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.05114767401827605</v>
+        <v>0.01420130949272009</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,31 +5165,31 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1159417995917212</v>
+        <v>0.05050286419588784</v>
       </c>
       <c r="BN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01324806452932358</v>
+        <v>0.04567363497240733</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1293488856416807</v>
+        <v>0.06414937971360662</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2091406594477493</v>
+        <v>0.243771273995952</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.04920408589634243</v>
+        <v>-0.1889681294405231</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.007842033343542358</v>
+        <v>-0.05717622620859933</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,25 +5228,25 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.06682447171281752</v>
+        <v>-0.06120787049837915</v>
       </c>
       <c r="CF9" t="n">
         <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01075434402733182</v>
+        <v>0.1239575032827003</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.004597510246866055</v>
+        <v>0.02779152522301154</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5255,25 +5255,25 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.06652229576239554</v>
+        <v>-0.1396752535031718</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.08652100095011309</v>
+        <v>0.2123801622211874</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.09731815015240408</v>
+        <v>0.1045732220639593</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
@@ -5282,49 +5282,49 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.04674449513566128</v>
+        <v>-0.05640382645088705</v>
       </c>
       <c r="CX9" t="n">
         <v>-0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.03297989439050351</v>
+        <v>0.1323328769347906</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.02200864023312033</v>
+        <v>0.04688076261877952</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01039655936482607</v>
+        <v>-0.01597210100195101</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.05056160036573332</v>
+        <v>0.02482375449347824</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01677728753732124</v>
+        <v>-0.05573364018611491</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,154 +5336,154 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.07305759478620687</v>
+        <v>-0.09209261834093206</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.006548244747438567</v>
+        <v>0.03989860296513642</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01087150994443488</v>
+        <v>-0.01361246223883445</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.01970852078471088</v>
+        <v>-0.009035996945877745</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.04517395205805196</v>
+        <v>0.06154849846761319</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.00176352936055005</v>
+        <v>-0.0213167419591277</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.01946773999066088</v>
+        <v>0.01970208112190847</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.05589028958343661</v>
+        <v>0.09767514918615754</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.05186427356356711</v>
+        <v>0.04322985340754337</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.06913686737091121</v>
+        <v>-0.05055765014021263</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.0434742363579053</v>
+        <v>-0.1272768848230472</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.003882223424439064</v>
+        <v>0.002494039541653837</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.05489366252415716</v>
+        <v>-0.07927184682708677</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.02525235982601611</v>
+        <v>0.1489606113796301</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.01653577452264238</v>
+        <v>0.03035725230868063</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.04132604334015316</v>
+        <v>-0.06034830290860169</v>
       </c>
       <c r="FI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04045276436798557</v>
+        <v>0.0268316027284342</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.02381428549548505</v>
+        <v>0.02276903476738497</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
@@ -5492,61 +5492,61 @@
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.01906614215213652</v>
+        <v>0.03742089127418233</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.01088487008680054</v>
+        <v>0.1055719887335693</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.05696236315212239</v>
+        <v>-0.2060998720222946</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.03136543091567279</v>
+        <v>-0.0251467753603013</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.02336920943400334</v>
+        <v>0.04316929440006134</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1963888317397002</v>
+        <v>0.173399881702218</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.04709216756717428</v>
+        <v>-0.0778387070069796</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0660938898972266</v>
+        <v>-0.07304971076821971</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,25 +5572,25 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.001161765586989041</v>
+        <v>-0.002655463211428131</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07274978047766571</v>
+        <v>0.0951817762946872</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.007316443804574147</v>
+        <v>-0.01421359661554822</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0576308701596359</v>
+        <v>-0.05216678771744932</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,52 +5599,52 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.008892036673764927</v>
+        <v>0.001510864441348078</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0565734863258672</v>
+        <v>0.03164081257410128</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.01566991730746146</v>
+        <v>-0.02127021004390413</v>
       </c>
       <c r="W10" t="n">
-        <v>0.002130376963811484</v>
+        <v>-0.03737440433143588</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.004642631526706929</v>
+        <v>0.004113401866384319</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01313322588710642</v>
+        <v>-0.02716645581425617</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.07980571240793881</v>
+        <v>-0.05389053179688321</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.001448646569227007</v>
+        <v>-0.1452946468163987</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.006067580184431428</v>
+        <v>0.01560437024449493</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -5662,25 +5662,25 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.003642976906166457</v>
+        <v>0.1264234024947394</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.02683920191352007</v>
+        <v>-0.01890125556375615</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.06812710205361365</v>
+        <v>0.03764154441314937</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0006352810120921335</v>
+        <v>-0.0103560939590083</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3778408537145731</v>
+        <v>0.2324902631163412</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.05808602026277358</v>
+        <v>-0.04055531153376234</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1420670069417487</v>
+        <v>-0.1971983439818922</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,7 +5707,7 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.07201765368908028</v>
+        <v>-0.03402801586591719</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.006081587597940999</v>
+        <v>-0.0139468909496445</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.02401650059834471</v>
+        <v>-0.03026826212638277</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1097513984975771</v>
+        <v>-0.01556170206057348</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.00980928607467927</v>
+        <v>-0.01019530179268359</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1271440061519723</v>
+        <v>0.03412372093479525</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.08784180950691396</v>
+        <v>0.05935335040412738</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.09366737778771339</v>
+        <v>0.0474117481920236</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.04702949776176625</v>
+        <v>0.00477601667376824</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,52 +5770,52 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1984504628747574</v>
+        <v>0.1969917439424146</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.03195835068662787</v>
+        <v>-0.07973941342648731</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01317106231699266</v>
+        <v>-0.1184175406144688</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.006164865489002822</v>
+        <v>-0.04489633708236853</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.05760472672322049</v>
+        <v>-0.06693340866730173</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01543284939471905</v>
+        <v>0.06817767853165668</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.002985508181212015</v>
+        <v>0.02578529531372405</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.007261988499787183</v>
+        <v>-0.006577152843682286</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
@@ -5824,79 +5824,79 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.06504893508187176</v>
+        <v>-0.06424128703990206</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.07775483964113833</v>
+        <v>0.09343333654849061</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.01357818368182012</v>
+        <v>0.1369204001527551</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.06739601905163875</v>
+        <v>0.05135404988229628</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.03575826774867429</v>
+        <v>-0.06753186389981083</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.03021135801010719</v>
+        <v>0.08140642133182148</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.002051885915202483</v>
+        <v>0.03800414432881152</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.009335254323989808</v>
+        <v>-0.009775298451110494</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.07852314802316002</v>
+        <v>-0.05310897649448094</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.02574650772531148</v>
+        <v>0.025775061832946</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.008309121798264985</v>
+        <v>-0.01462702947700577</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.01565595945951516</v>
+        <v>-0.01176545792565011</v>
       </c>
       <c r="DM10" t="n">
         <v>0</v>
@@ -5905,106 +5905,106 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.08376270572958185</v>
+        <v>-0.05997544980132988</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.001429921646980044</v>
+        <v>0.03114773778937607</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0609313776828176</v>
+        <v>-0.06484186225723743</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.03106372032243052</v>
+        <v>0.1077082445070858</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.03145902521789398</v>
+        <v>0.04308225303376392</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.01929820211751973</v>
+        <v>0.06664562663088019</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.01295866256373441</v>
+        <v>-0.04315188860710132</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.01010165454218405</v>
+        <v>0.08702158647979746</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02650961021065359</v>
+        <v>-0.003106325999018117</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.02250592040568511</v>
+        <v>0.04365681111472815</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.001804784518184221</v>
+        <v>1.686901342820741e-05</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.06579628951356771</v>
+        <v>-0.0195501174843997</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.07769628066352072</v>
+        <v>-0.03300115466412621</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.03365537408573628</v>
+        <v>0.06906561634386524</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.05227769851540773</v>
+        <v>-0.004710757401190575</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.007445584190673795</v>
+        <v>-0.005508538859543915</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
@@ -6013,106 +6013,106 @@
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.0422938659557277</v>
+        <v>-0.08532963338379124</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.02134142821430277</v>
+        <v>0.08139912081736381</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01926591161491184</v>
+        <v>0.02706773089328519</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.003718923184338588</v>
+        <v>-0.007554923111766673</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.05314849434634956</v>
+        <v>-0.0303573101862637</v>
       </c>
       <c r="FI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.04369102303571347</v>
+        <v>-0.008009178658892384</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.02543611997279649</v>
+        <v>0.07227489112768083</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.009262878205955951</v>
+        <v>-0.04339894433744962</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.09917365867758697</v>
+        <v>-0.001815238173325689</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.04724614066371533</v>
+        <v>0.1148282995311383</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.05693493423576548</v>
+        <v>-0.1341190320132236</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.005533057103784433</v>
+        <v>0.01252381782166864</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.04193475124697744</v>
+        <v>-0.02288797331778608</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.04685213718298723</v>
+        <v>-0.004925111916136243</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.02693143949956142</v>
+        <v>-0.05012074382631843</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,25 +6123,25 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.05088422737026656</v>
+        <v>0.3203850597686319</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
         <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.04662616020380753</v>
+        <v>0.03496369977932117</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.04260496950571607</v>
+        <v>-0.2096781333544276</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,22 +6150,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01554639725378135</v>
+        <v>0.2237377159386557</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02738061497810105</v>
+        <v>-0.03767399484032105</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.01842593334583093</v>
+        <v>-0.08916693349915196</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6174,10 +6174,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.003729754445366649</v>
+        <v>0.06878750345158882</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,16 +6186,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.000343298706036287</v>
+        <v>-0.0519941951769266</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01105648541849916</v>
+        <v>0.002593373496965915</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>-0</v>
@@ -6204,19 +6204,19 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01706402026879935</v>
+        <v>-0.06162052984202698</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0132209299976217</v>
+        <v>-0.2330814433275613</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01492292994150448</v>
+        <v>0.04785310664341542</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.01260418325001941</v>
+        <v>0.1024564154890766</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,43 +6240,43 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.01827773511281554</v>
+        <v>0.02291166261132754</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.004969483240315772</v>
+        <v>-0.04907574529907056</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.07137844818757089</v>
+        <v>0.4458629021018263</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.02049143744422375</v>
+        <v>-0.2338089036766871</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.008600660976040011</v>
+        <v>-0.07105476827822309</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB11" t="n">
         <v>0</v>
@@ -6285,34 +6285,34 @@
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.01428794610243614</v>
+        <v>-0.005693280405702348</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.02528321707322836</v>
+        <v>-0.004460028150851017</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.02315550056779115</v>
+        <v>-0.07148480117524716</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.04555731069739045</v>
+        <v>0.1073750994842585</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
@@ -6321,16 +6321,16 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.02657758234767166</v>
+        <v>0.1335119080022379</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.007044678167242642</v>
+        <v>0.1056101234289199</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.02891066813923194</v>
+        <v>0.3575456531665435</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,40 +6348,40 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01500050528803895</v>
+        <v>-0.03972560544179492</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.0102694219436271</v>
+        <v>-0.08170174231537536</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.008241183682495682</v>
+        <v>-0.1375237590769235</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01172941140661079</v>
+        <v>-0.02359073480347052</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.01234410546329418</v>
+        <v>0.1006518589917089</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.01056245848983137</v>
+        <v>-0.1967899870782856</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
@@ -6402,13 +6402,13 @@
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.006344661963413933</v>
+        <v>0.07010897738971374</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.0103157850051508</v>
+        <v>0.01146903024419316</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>0</v>
@@ -6420,22 +6420,22 @@
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.0007597373336532584</v>
+        <v>-0.1194255432114757</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01136663158488271</v>
+        <v>-0.02896737550667297</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0143160965818445</v>
+        <v>0.09908213829249082</v>
       </c>
       <c r="DB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC11" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.003199541900963916</v>
+        <v>-0.1070114885941063</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,37 +6456,37 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.007915369066963718</v>
+        <v>-0.1454222970144925</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.008389688680924422</v>
+        <v>0.02345380880018008</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.01121163402739042</v>
+        <v>-0.09588198234276232</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02289052293737456</v>
+        <v>-0.0205614708329357</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.0184465961696868</v>
+        <v>-0.006447631898080123</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6501,22 +6501,22 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.007994465400925592</v>
+        <v>0.05876284630607714</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.0159356582980556</v>
+        <v>-0.02883505292571303</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.006331989432545536</v>
+        <v>0.06433034846044633</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
         <v>-0</v>
@@ -6528,52 +6528,52 @@
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.003454075371637467</v>
+        <v>0.01817609732883844</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
         <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.001927054227620378</v>
+        <v>-0.08779970265865891</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.003971169978966549</v>
+        <v>0.07683985563393253</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01023628583621639</v>
+        <v>-0.01939933598477205</v>
       </c>
       <c r="EQ11" t="n">
         <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.007662274409186009</v>
+        <v>-0.2198728402454622</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01661470225983813</v>
+        <v>0.05789169562957716</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
@@ -6582,22 +6582,22 @@
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.001179725996483157</v>
+        <v>-0.1483392128530679</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01112677033235319</v>
+        <v>-0.0554135022545758</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.01523224530743077</v>
+        <v>0.07643407004422055</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
@@ -6609,34 +6609,34 @@
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.01639941906374026</v>
+        <v>-0.1424182761907809</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.026538365169214</v>
+        <v>0.1414491799808072</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.009580502603946179</v>
+        <v>0.08194794499707285</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.00216623408517078</v>
+        <v>0.0974978736929253</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
@@ -6645,25 +6645,25 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.004155120770520443</v>
+        <v>-0.05988399479783202</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.02229382895698604</v>
+        <v>-0.007889618451377155</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.02365341256166117</v>
+        <v>-0.04539356342723556</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.003216521487811536</v>
+        <v>0.1071807815694824</v>
       </c>
       <c r="GE11" t="n">
         <v>0</v>
@@ -6692,70 +6692,70 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1423376139341109</v>
+        <v>0.2649087386532697</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.07977176027808842</v>
+        <v>-0.1309540889221403</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04077158497361084</v>
+        <v>-0.01176112652614782</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06185123938747884</v>
+        <v>0.1721703183792813</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.02845477087287192</v>
+        <v>-0.05836294640698933</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.03200115242546667</v>
+        <v>-0.02257178601194192</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
         <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02729571744941701</v>
+        <v>0.04941205756698331</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.005183910959786354</v>
+        <v>-0.01243339254194276</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02781124403146261</v>
+        <v>-0.03075960413185706</v>
       </c>
       <c r="X12" t="n">
         <v>-0</v>
@@ -6770,82 +6770,82 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.06141740763797891</v>
+        <v>-0.06769435179696384</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>7.535821847556842e-06</v>
+        <v>-0.1020284963402123</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02656949515727248</v>
+        <v>-0.05164329215423546</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.009761085692321331</v>
+        <v>0.09180676458056071</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04355224595495289</v>
+        <v>-0.07948547635766522</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.05997574280939665</v>
+        <v>0.06830061923049949</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.274798010452482</v>
+        <v>0.248153302616088</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.00680001084798438</v>
+        <v>-0.100235982329072</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.11009734283771</v>
+        <v>-0.1123526617808172</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,16 +6854,16 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.01901537083110226</v>
+        <v>0.003367654054046487</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.02324111994000254</v>
+        <v>-0.009739385094061515</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.06918554038629127</v>
+        <v>-0.01337117089053904</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.07854668311012042</v>
+        <v>-0.01146158641860911</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.03445853059375985</v>
+        <v>0.03759097187684315</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.09128832380920518</v>
+        <v>0.06819608759976228</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,43 +6908,43 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1306336970622737</v>
+        <v>0.2158628374270325</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.005812360802558484</v>
+        <v>-0.09141979118721859</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0474077713994423</v>
+        <v>-0.01630734078860252</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.03222615042392333</v>
+        <v>-0.09337474284298647</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.00265267296181831</v>
+        <v>0.0968586683322588</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.008215937771632102</v>
+        <v>-0.008600101189557412</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6956,25 +6956,25 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.03922253786284939</v>
+        <v>-0.0764053214851655</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.0947637635616735</v>
+        <v>0.1388707302039459</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.07134997740990118</v>
+        <v>0.01807942537486989</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,49 +6989,49 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.01257595754050121</v>
+        <v>-0.09175938063587132</v>
       </c>
       <c r="CX12" t="n">
         <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.01051749832651136</v>
+        <v>0.0983069252233659</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.0004379591942163296</v>
+        <v>0.0004016952249104669</v>
       </c>
       <c r="DA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.005914582562408634</v>
+        <v>-0.09834181332689587</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01322607681135546</v>
+        <v>0.01233040598558303</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0304810504014051</v>
+        <v>-0.04590099603567923</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,103 +7043,103 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.04553137371967172</v>
+        <v>-0.07138468329681386</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.001458382273143752</v>
+        <v>0.03689644081004063</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01351492163736432</v>
+        <v>-0.006250851853048756</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.02886764613896166</v>
+        <v>0.005049430602823046</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.04359012386214803</v>
+        <v>-0.05400382446209758</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.006855443921252537</v>
+        <v>0.07346046397902942</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.008936361021248545</v>
+        <v>-0.04846387196853273</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.04467586409733042</v>
+        <v>0.06725187930706529</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.02912530493987553</v>
+        <v>0.03547199443176016</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.02580589634731654</v>
+        <v>-0.02767880590028623</v>
       </c>
       <c r="EQ12" t="n">
         <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.007066738349484889</v>
+        <v>0.05794146661686649</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.04575154623235506</v>
+        <v>-0.04560764162768107</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,73 +7151,73 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.01999897762334274</v>
+        <v>-0.1064115602559293</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.007937183751607143</v>
+        <v>0.1132678043339104</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.00517317056787432</v>
+        <v>-0.01558886413421766</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.04255740021295755</v>
+        <v>-0.1004341632423126</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.03189159342688888</v>
+        <v>0.06034122737496714</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.03434307018281231</v>
+        <v>0.04362586017917549</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.02602090395329862</v>
+        <v>-0.00218065028549442</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.01129041019804636</v>
+        <v>0.1064305592532512</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.06068425986102815</v>
+        <v>-0.0402941056826215</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
@@ -7226,31 +7226,31 @@
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.002636499121179018</v>
+        <v>-0.08829484250967241</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.03324604392374255</v>
+        <v>0.05071761097251411</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7258,22 +7258,22 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2082683930368853</v>
+        <v>0.4029566871762625</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.06375650188876804</v>
+        <v>0.02380161055598261</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2117228092788586</v>
+        <v>-0.3518953977988109</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7288,19 +7288,19 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1050389205360323</v>
+        <v>0.3582035856994764</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.03327051818567936</v>
+        <v>-0.04601008899225231</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1201182400168432</v>
+        <v>-0.2119986371781902</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -7315,25 +7315,25 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.03780997725553679</v>
+        <v>0.1260369488564336</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.008722438135098898</v>
+        <v>-0.1735905702576053</v>
       </c>
       <c r="X13" t="n">
-        <v>0.005790987790791963</v>
+        <v>-0.01434642295688373</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,34 +7342,34 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.04023163991214278</v>
+        <v>-0.05117449290699277</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.05122989758444805</v>
+        <v>-0.3741660379556105</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.01364885071176709</v>
+        <v>-0.1913062575284432</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.04809967242120859</v>
+        <v>0.1610808425749926</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01259911392770426</v>
+        <v>0.02167031884099715</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.0342630406277934</v>
+        <v>-0.1894421933146263</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,37 +7393,37 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2271570285059828</v>
+        <v>0.8979275694619016</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.03308015546548732</v>
+        <v>-0.2236181933658839</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.1171475256239546</v>
+        <v>-0.1607439786613882</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04111646289764616</v>
+        <v>-0.1136943675475972</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,70 +7432,70 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.05272237749003173</v>
+        <v>-0.1857683192290056</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.06428950543942756</v>
+        <v>-0.1874824346591174</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.07827977687061109</v>
+        <v>0.1243330894635756</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0286820387502836</v>
+        <v>0.1003357016696279</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01623858503681848</v>
+        <v>0.06913353738660072</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1023560511815254</v>
+        <v>0.4850493833437895</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.03521798697448252</v>
+        <v>-0.1698945630907757</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.0673496856355162</v>
+        <v>-0.2461869709707446</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
@@ -7504,46 +7504,46 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.04837355089524972</v>
+        <v>-0.1790393624505461</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.006032563050427635</v>
+        <v>0.02561924442012598</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.05720042609349833</v>
+        <v>0.1666287522467877</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.03190735006837831</v>
+        <v>-0.3890955113559509</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.01432840717548467</v>
+        <v>0.460762535018405</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01458301566003884</v>
+        <v>0.3375542367676162</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7558,19 +7558,19 @@
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.03350740995258061</v>
+        <v>-0.1585498411040424</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.0002243354326567019</v>
+        <v>-0.007491061977655872</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.05697631735417204</v>
+        <v>0.148903179764393</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7585,46 +7585,46 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.02609890053429786</v>
+        <v>-0.004762857186775647</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.03131498071785965</v>
+        <v>-0.1469191685890011</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.003610245553892122</v>
+        <v>-0.02379953100121293</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.01169343238306582</v>
+        <v>-0.009455005849959324</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0265645309463354</v>
+        <v>-0.02542057899672572</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.01113018941792248</v>
+        <v>0.1771484808410823</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7639,25 +7639,25 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.001745401594954228</v>
+        <v>0.1047482894156048</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.009990127479827133</v>
+        <v>-0.02183655772827135</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01135707984918953</v>
+        <v>0.08165408020668626</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
@@ -7666,34 +7666,34 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.01739968801291407</v>
+        <v>-0.06026215616786849</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.006761034547527117</v>
+        <v>-0.06076790520790758</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.05649117272818741</v>
+        <v>-0.01430069906126644</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.004098780519732675</v>
+        <v>-0.05225661699926173</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.02180323998135616</v>
+        <v>-0.08410255142470613</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.07445597326565336</v>
+        <v>0.1188541551540371</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
         <v>-0</v>
@@ -7720,46 +7720,46 @@
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.02877208528394599</v>
+        <v>-0.1954053477133302</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.003252490427985623</v>
+        <v>-0.03563846506143202</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.05762694983149293</v>
+        <v>0.1457702629593748</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.04644390526991651</v>
+        <v>-0.1774531919153998</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.005172750907853462</v>
+        <v>0.1172340696494561</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.01069416418642537</v>
+        <v>-0.05132085104277713</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
@@ -7771,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.007529305302884922</v>
+        <v>0.06642445261296567</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,43 +7783,43 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.01537711238319511</v>
+        <v>0.07546831995781761</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01092454787956327</v>
+        <v>-0.008424872919707293</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.03499241732656223</v>
+        <v>-0.06512638008263948</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.02219470663159102</v>
+        <v>0.02619651908969712</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7830,22 +7830,22 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2658142024411848</v>
+        <v>0.1969943296585131</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.08844000622542239</v>
+        <v>-0.1230041922407553</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0303337345132809</v>
+        <v>-0.07664195082296106</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
         <v>-0</v>
@@ -7857,16 +7857,16 @@
         <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1114685850028958</v>
+        <v>0.1181176013018847</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.04440778300697951</v>
+        <v>-0.08025109957809951</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02737057531133096</v>
+        <v>-0.08510380127929111</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7881,82 +7881,82 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.07124069638303114</v>
+        <v>0.05108134704201272</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.005545154996276699</v>
+        <v>-0.02133443759715777</v>
       </c>
       <c r="W14" t="n">
-        <v>0.03567495769414521</v>
+        <v>-0.02839926439731848</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.04585454714499416</v>
+        <v>-0.02250571975653677</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.02393470636313099</v>
+        <v>-0.1126361400370858</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.00124978140176754</v>
+        <v>-0.1157247733033327</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.008593599821629386</v>
+        <v>0.130108939108669</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.04471494117065683</v>
+        <v>-0.03460723706358117</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.06084082604698101</v>
+        <v>0.06296020093124591</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
@@ -7965,25 +7965,25 @@
         <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.3176368210062613</v>
+        <v>0.2343760798164134</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.02777873791666254</v>
+        <v>-0.0172594447610984</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.08028187864384435</v>
+        <v>-0.1929847185936406</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,25 +7992,25 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.004428305130310448</v>
+        <v>-0.0284316554293867</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.04787155000096897</v>
+        <v>-0.02525011535224286</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.05501520270558227</v>
+        <v>0.003932930901988556</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
@@ -8019,22 +8019,22 @@
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.07421728747577544</v>
+        <v>0.04047282325367915</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.02775096421140116</v>
+        <v>0.02112171883699198</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.13271862716799</v>
+        <v>0.07768054440461662</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8043,22 +8043,22 @@
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.1595955711887366</v>
+        <v>0.2160461237909589</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.03420812550903161</v>
+        <v>-0.09193398294082324</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.04943519654606635</v>
+        <v>-0.04902734885198927</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8067,22 +8067,22 @@
         <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.06506070977038533</v>
+        <v>-0.07546909332789979</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0007917568171594626</v>
+        <v>0.07338233525307181</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.008014943975894206</v>
+        <v>0.0344444120086948</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
@@ -8100,43 +8100,43 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.04070923786284401</v>
+        <v>-0.1186236085908391</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.06521182499532691</v>
+        <v>0.1532977441529411</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.08100228598146601</v>
+        <v>0.0478523529283731</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT14" t="n">
         <v>-0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.04847469463313332</v>
+        <v>-0.0636431449704938</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.01328769099371923</v>
+        <v>0.08350370566970751</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.007226279540931068</v>
+        <v>0.03934996806578833</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
@@ -8154,22 +8154,22 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.002081591294739958</v>
+        <v>0.001279048353687449</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.01414824553634402</v>
+        <v>0.01533841424156677</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.03660736736504783</v>
+        <v>-0.03712060633556868</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
@@ -8181,46 +8181,46 @@
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.03671861429088408</v>
+        <v>-0.07188537391858839</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.03646744251611977</v>
+        <v>-0.02957846223755578</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.02875041856342961</v>
+        <v>0.004959671019749133</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.04396515287277595</v>
+        <v>0.09123828326864399</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.002425467162184072</v>
+        <v>0.05072541447968836</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.05892374371240745</v>
+        <v>-0.09371196403981619</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
         <v>0</v>
@@ -8229,31 +8229,31 @@
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.05428567356525135</v>
+        <v>0.01150378946089687</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.02297163381942645</v>
+        <v>0.05027537815203768</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.04434475476480226</v>
+        <v>0.05605868341284426</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
@@ -8262,22 +8262,22 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.04023258233721248</v>
+        <v>-0.05837261167767527</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.02199205398607292</v>
+        <v>0.09584021870770892</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02305875829036689</v>
+        <v>-0.02468609169697563</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8286,25 +8286,25 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.05159489866377343</v>
+        <v>-0.08269903511361394</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.007028688744867008</v>
+        <v>0.09286130470986631</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.009725004036318053</v>
+        <v>0.02251715870817579</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
@@ -8313,46 +8313,46 @@
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.02826247570419597</v>
+        <v>0.02222490478207157</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.02038722299721847</v>
+        <v>0.004818872154196017</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.05258436081302831</v>
+        <v>-0.05189243639250889</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.004576613409570957</v>
+        <v>0.0001628442246947332</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.002681039023099751</v>
+        <v>0.05062507618446797</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.00197772979527345</v>
+        <v>-0.03888668080450423</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8370,25 +8370,25 @@
         <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.001315376899869805</v>
+        <v>-0.03820788583232679</v>
       </c>
       <c r="GA14" t="n">
         <v>-0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.05129883432872734</v>
+        <v>0.03757268913231938</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
         <v>-0</v>
@@ -8399,22 +8399,22 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5266021588927218</v>
+        <v>0.4592999313798046</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1640017068662213</v>
+        <v>-0.2490689928645447</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1279443253964925</v>
+        <v>0.07431037000380902</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
         <v>-0</v>
@@ -8426,22 +8426,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.320055300372456</v>
+        <v>0.3401903606468935</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.09878446166527016</v>
+        <v>-0.1579139308354817</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.09473462689504948</v>
+        <v>0.01928632094557174</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8450,52 +8450,52 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1423070113031956</v>
+        <v>0.1223177037716113</v>
       </c>
       <c r="U15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.02492199349995443</v>
+        <v>-0.04482349206841679</v>
       </c>
       <c r="W15" t="n">
-        <v>0.06081868542387327</v>
+        <v>-0.04622409545257102</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1393724720647356</v>
+        <v>-0.05792954526837121</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.03101141262982495</v>
+        <v>-0.2404711558251086</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.04488794258117005</v>
+        <v>0.01159512454008826</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
@@ -8507,16 +8507,16 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.05937754926682922</v>
+        <v>0.1467841672453001</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.03500685268577598</v>
+        <v>-0.0913446443741797</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.03769240743162394</v>
+        <v>0.1573363079079172</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.480820414121337</v>
+        <v>0.4096054783478425</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.01366642686026473</v>
+        <v>-0.2113207787369872</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1355266361698516</v>
+        <v>-0.1267850142194464</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
@@ -8555,22 +8555,22 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.05023494578373507</v>
+        <v>-0.01406266420109043</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.06218417465801268</v>
+        <v>-0.05812816284275535</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1765210031858296</v>
+        <v>-0.02199595742848238</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -8579,7 +8579,7 @@
         <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,22 +8588,22 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.03369124413156706</v>
+        <v>-0.02176649388829075</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.04651568544356714</v>
+        <v>0.0356570982730414</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.05366883780210871</v>
+        <v>0.01617702374505986</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
@@ -8615,22 +8615,22 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2967715995765287</v>
+        <v>0.323911744477151</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0.02398865665440974</v>
+        <v>-0.112587136437876</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.08041722167175092</v>
+        <v>-0.003425305170592014</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
         <v>0</v>
@@ -8639,79 +8639,79 @@
         <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1126547114327314</v>
+        <v>-0.146218037601777</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.03167684963237419</v>
+        <v>0.1507734828980468</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.02338070521963049</v>
+        <v>-0.04945065591748327</v>
       </c>
       <c r="CI15" t="n">
         <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.05997478264077277</v>
+        <v>-0.1313354871852221</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.07537933526084278</v>
+        <v>0.2473905480404258</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.2028444542700986</v>
+        <v>0.08723447726255916</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
         <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.1047563413041842</v>
+        <v>-0.1376640233325424</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.04313673549552657</v>
+        <v>0.1585073335693134</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.0234636225849804</v>
+        <v>-0.03031628049879435</v>
       </c>
       <c r="DA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>-0</v>
@@ -8723,19 +8723,19 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.04390413049359589</v>
+        <v>-0.03268544792005892</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.0253489655967313</v>
+        <v>0.006232582998154094</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.0005791039608123506</v>
+        <v>0.004910379772544295</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK15" t="n">
         <v>-0</v>
@@ -8747,22 +8747,22 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.05639427581119737</v>
+        <v>-0.08886984690951184</v>
       </c>
       <c r="DP15" t="n">
         <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.01394998892921293</v>
+        <v>0.07892409309937623</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.06483379505586852</v>
+        <v>-0.01267760183668199</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
@@ -8777,76 +8777,76 @@
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.087696568214662</v>
+        <v>-0.008879431562831944</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.041392214715383</v>
+        <v>-0.06167336487110959</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01122381908727825</v>
+        <v>0.05207706628624637</v>
       </c>
       <c r="EB15" t="n">
         <v>0</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
         <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.08397011838132298</v>
+        <v>-0.1040115757992974</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.0476783766729412</v>
+        <v>0.1287848172394728</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0473519155327896</v>
+        <v>0.01503957307790874</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.07999527011193122</v>
+        <v>-0.0980634279966893</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.03224407894232596</v>
+        <v>0.02431518550499255</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.03696149486387608</v>
+        <v>-0.02513090388549883</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8855,25 +8855,25 @@
         <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.1135123195217177</v>
+        <v>-0.1690299288172035</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.05158105808760149</v>
+        <v>0.1683011734379732</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.02925566852405522</v>
+        <v>-0.05159104066845055</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
@@ -8882,85 +8882,85 @@
         <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0008250227778748072</v>
+        <v>-0.1090119207004888</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.05605846725439557</v>
+        <v>0.1550242885673343</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.040488808863057</v>
+        <v>-0.0717564193471827</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN15" t="n">
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.01320677788012985</v>
+        <v>-0.02808628697783429</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0.1566711433950182</v>
+        <v>-0.2286003821125804</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.02443630720108927</v>
+        <v>-0.02209768430268495</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.04887855143779864</v>
+        <v>-0.1052575195230205</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.04367635706489357</v>
+        <v>0.08242939840948847</v>
       </c>
       <c r="GC15" t="n">
         <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -9534,10 +9534,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1805909505458108</v>
+        <v>0.4751807137473129</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,13 +9546,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.119757135033449</v>
+        <v>-0.05242841645694964</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.08884134337069356</v>
+        <v>-0.2243215235580401</v>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>-0</v>
@@ -9561,10 +9561,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.09863053854051963</v>
+        <v>0.505133143592046</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9573,52 +9573,52 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.08342195518723722</v>
+        <v>-0.1523875724861973</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.05035281700708783</v>
+        <v>-0.1139903551128226</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.02839674518521029</v>
+        <v>0.1343308327003624</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.02700827503345632</v>
+        <v>-0.1659279655389492</v>
       </c>
       <c r="X17" t="n">
-        <v>0.03384254261908982</v>
+        <v>-0.04267104139750885</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB17" t="n">
         <v>-0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.03101984601478562</v>
+        <v>-0.04535009108994616</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -9627,10 +9627,10 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01734352370907175</v>
+        <v>-0.2489464487184511</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.01289819928696652</v>
+        <v>-0.04811610756037023</v>
       </c>
       <c r="AH17" t="n">
         <v>-0</v>
@@ -9642,25 +9642,25 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.04502806674697888</v>
+        <v>0.1101578348478637</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01413341906313262</v>
+        <v>-0.06443562814848482</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.03045101266979072</v>
+        <v>-0.1331295279000413</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9672,34 +9672,34 @@
         <v>-0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1456810618960618</v>
+        <v>0.637693893073473</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.06979582406239619</v>
+        <v>-0.296740868503626</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.05807727909519973</v>
+        <v>-0.2447710347931965</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.03504079284001378</v>
+        <v>-0.1050883905489143</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,70 +9708,70 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.06353284421843143</v>
+        <v>-0.03421044930800562</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.01480781567765173</v>
+        <v>-0.01504698432011635</v>
       </c>
       <c r="BI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.05336549320485137</v>
+        <v>0.1074730826290928</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01824585529148105</v>
+        <v>0.1188544976245564</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.02662023860906572</v>
+        <v>0.0497817175654869</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.08579363474066128</v>
+        <v>0.3898228084141211</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.03256121882232398</v>
+        <v>-0.1646247271384877</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.00511600079913459</v>
+        <v>-0.1316563804202258</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
         <v>-0</v>
@@ -9780,22 +9780,22 @@
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.0244984520076432</v>
+        <v>-0.1682310201157979</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.01498253577460471</v>
+        <v>0.068445921834404</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.02562695755794661</v>
+        <v>0.08793824810930656</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
@@ -9807,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>6.627891929991673e-05</v>
+        <v>-0.2363015846280664</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,16 +9816,16 @@
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.004332184993231889</v>
+        <v>0.2616998552612674</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.02538868624417195</v>
+        <v>0.1089554687455365</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
         <v>0</v>
@@ -9834,19 +9834,19 @@
         <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.01597164260823258</v>
+        <v>-0.1542262878149107</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.01383602766343624</v>
+        <v>0.03167383759752517</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.032420473135727</v>
+        <v>0.09395495666520304</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
@@ -9861,76 +9861,76 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.004520505976371979</v>
+        <v>-0.01667971149121852</v>
       </c>
       <c r="DG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.01629331877687439</v>
+        <v>-0.1024885046493789</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.006042220580495805</v>
+        <v>-0.01744166491293968</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.01241097418629115</v>
+        <v>-0.0780759707107468</v>
       </c>
       <c r="DP17" t="n">
         <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.01271028291613422</v>
+        <v>-0.01906898670833312</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.03953180568499263</v>
+        <v>-0.01845692479102554</v>
       </c>
       <c r="DT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.003425704254077025</v>
+        <v>0.1450068424113937</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.03298081360929953</v>
+        <v>-0.1006885937241414</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0.02726025675934995</v>
+        <v>0.005158234456888254</v>
       </c>
       <c r="EC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
@@ -9939,79 +9939,79 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.02007934898499271</v>
+        <v>-0.02354371418634968</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.01995130043856921</v>
+        <v>-0.04923404103231649</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.02158868621875034</v>
+        <v>0.05905595412982566</v>
       </c>
       <c r="EL17" t="n">
         <v>-0</v>
       </c>
       <c r="EM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.008939666019566868</v>
+        <v>-0.03294516870221779</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.01123193958043677</v>
+        <v>-0.05403687123748793</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.03308196953085439</v>
+        <v>0.0643661100115735</v>
       </c>
       <c r="EU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.01292532374807581</v>
+        <v>-0.1742435281871031</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.01212214669600263</v>
+        <v>0.03543842121683265</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.031827459063419</v>
+        <v>0.0739649069450824</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
@@ -10023,34 +10023,34 @@
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.02083513733166165</v>
+        <v>-0.1062408490088848</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.03656439271964508</v>
+        <v>0.07575991560637244</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.02326612637362454</v>
+        <v>0.1004289174790015</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.002780942594954297</v>
+        <v>-0.01791885283529501</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
@@ -10059,43 +10059,43 @@
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.0005944142999298141</v>
+        <v>0.002482284421427805</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.007866227700682708</v>
+        <v>0.1465148114993588</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.009781561657324904</v>
+        <v>-0.1171222695861566</v>
       </c>
       <c r="GA17" t="n">
         <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.03438253771116049</v>
+        <v>0.03294242515183823</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>0</v>
@@ -10103,10 +10103,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1594766284703648</v>
+        <v>0.3107394528412212</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10115,13 +10115,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1329252848999152</v>
+        <v>-0.02379094836348752</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.04448218526393674</v>
+        <v>-0.1355169003457776</v>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>-0</v>
@@ -10130,10 +10130,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.08998019160260975</v>
+        <v>0.3541233716947792</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -10142,13 +10142,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.09759931877266345</v>
+        <v>-0.09320379284011387</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.02044764591193857</v>
+        <v>-0.05574498660094128</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -10157,10 +10157,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.02193592041128959</v>
+        <v>0.07464870813206995</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
@@ -10169,25 +10169,25 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.01245358891200482</v>
+        <v>-0.1010631822883147</v>
       </c>
       <c r="X18" t="n">
-        <v>0.03788342385734385</v>
+        <v>-0.02611320913227699</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB18" t="n">
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.03729457602776494</v>
+        <v>-0.02187225577736801</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -10196,13 +10196,13 @@
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.009269702535601733</v>
+        <v>-0.1651650899814195</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.01310479531898711</v>
+        <v>-0.01244866316067473</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>-0</v>
@@ -10211,25 +10211,25 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.03659374481380514</v>
+        <v>0.06624754956390488</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.0231419591244449</v>
+        <v>-0.04092754021547024</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.02199431009327391</v>
+        <v>-0.09668570554271175</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10241,34 +10241,34 @@
         <v>-0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1313398970921783</v>
+        <v>0.4162956628623258</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.07520594017903466</v>
+        <v>-0.1669924405315783</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.02671163326343496</v>
+        <v>-0.1457962674793128</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>-0</v>
       </c>
       <c r="BC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.04108175352017904</v>
+        <v>-0.08444097508196684</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,79 +10277,79 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.06802883203649628</v>
+        <v>-0.03642114742642075</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.01403813570297423</v>
+        <v>-0.00656823479168984</v>
       </c>
       <c r="BI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.05872391796566601</v>
+        <v>0.0919310017615779</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.01851558757690041</v>
+        <v>0.09984583669550512</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.03339521859580979</v>
+        <v>0.06000153314764341</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
         <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.08136471602880752</v>
+        <v>0.2501380315663227</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.03312344087486192</v>
+        <v>-0.09922592164773496</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.03083289277350489</v>
+        <v>-0.08261169399207878</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
         <v>-0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.02130610835744444</v>
+        <v>-0.1078099778788614</v>
       </c>
       <c r="CF18" t="n">
         <v>-0</v>
@@ -10358,13 +10358,13 @@
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.02141255218833173</v>
+        <v>0.04093961522389573</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.0159278986777816</v>
+        <v>0.06205883861801632</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
@@ -10376,22 +10376,22 @@
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.01597221599425114</v>
+        <v>-0.1546023868516013</v>
       </c>
       <c r="CO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP18" t="n">
         <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.003215959779684014</v>
+        <v>0.1539982201382763</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.01161389374216703</v>
+        <v>0.06321268934191197</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
         <v>-0</v>
@@ -10403,46 +10403,46 @@
         <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.01083296888672765</v>
+        <v>-0.09593160198586907</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.02023894689366489</v>
+        <v>0.01207592648526907</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.0219026782825113</v>
+        <v>0.06489566780947632</v>
       </c>
       <c r="DB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD18" t="n">
         <v>0</v>
       </c>
       <c r="DE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.009643233759765701</v>
+        <v>-0.01024847404452254</v>
       </c>
       <c r="DG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.0008687467360901396</v>
+        <v>-0.01658326388576798</v>
       </c>
       <c r="DJ18" t="n">
-        <v>-0.002347598804516344</v>
+        <v>-0.01979863711563454</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10451,28 +10451,28 @@
         <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.01757166100786484</v>
+        <v>-0.04534999320370089</v>
       </c>
       <c r="DP18" t="n">
         <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.018640285075802</v>
+        <v>-0.0181480723459955</v>
       </c>
       <c r="DS18" t="n">
-        <v>-0.04137250354818391</v>
+        <v>-0.0375459773899049</v>
       </c>
       <c r="DT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU18" t="n">
         <v>-0</v>
@@ -10481,49 +10481,49 @@
         <v>-0</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.003632048494903749</v>
+        <v>0.0858776790926874</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.03330487975199659</v>
+        <v>-0.08951397277809087</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.03959031922436181</v>
+        <v>-0.03015312836328703</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
       </c>
       <c r="ED18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE18" t="n">
         <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.01613654537462064</v>
+        <v>-0.01326894603149913</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.0225330151011567</v>
+        <v>-0.03495848013557177</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.008779198302858915</v>
+        <v>0.05262866243233656</v>
       </c>
       <c r="EL18" t="n">
         <v>-0</v>
@@ -10532,40 +10532,40 @@
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.01879030841851152</v>
+        <v>-0.02612511592864977</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.0128178064215555</v>
+        <v>-0.02959621371303659</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.03580474841507018</v>
+        <v>0.04864061803229485</v>
       </c>
       <c r="EU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.008106503164205204</v>
+        <v>-0.1061924445795412</v>
       </c>
       <c r="EZ18" t="n">
         <v>-0</v>
@@ -10574,52 +10574,52 @@
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.01716808708465802</v>
+        <v>0.02101335644220511</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.02517334330630188</v>
+        <v>0.04829582153201901</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF18" t="n">
         <v>-0</v>
       </c>
       <c r="FG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.02225973300368827</v>
+        <v>-0.06091034014435358</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.03758052242785725</v>
+        <v>0.02422752788228083</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.01495859759987209</v>
+        <v>0.06581819679159399</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.003240496908412143</v>
+        <v>-0.01982929961819309</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,43 +10628,43 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.001350213516820499</v>
+        <v>0.0001924365838319898</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.0001879338681029824</v>
+        <v>0.07591494059395631</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.02804983449652767</v>
+        <v>-0.08010113207279335</v>
       </c>
       <c r="GA18" t="n">
         <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.03062155874100828</v>
+        <v>0.01390764876644941</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
       </c>
       <c r="GF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG18" t="n">
         <v>0</v>
